--- a/figures_updated/Fig5_stats.xlsx
+++ b/figures_updated/Fig5_stats.xlsx
@@ -435,19 +435,19 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.00874631501125725</v>
+        <v>-0.0165562358618992</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00814955283623907</v>
+        <v>0.0080502557090084</v>
       </c>
       <c r="D2" t="n">
-        <v>64.2867468324853</v>
+        <v>64.4427038225849</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.07322637045367</v>
+        <v>-2.05660993393942</v>
       </c>
       <c r="F2" t="n">
-        <v>0.287181679230464</v>
+        <v>0.043777138936302</v>
       </c>
     </row>
     <row r="3">
@@ -455,16 +455,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00584200201334314</v>
+        <v>0.00585844740693992</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0000358701365596865</v>
+        <v>0.0000365982246002697</v>
       </c>
       <c r="D3" t="n">
-        <v>17874.4399702946</v>
+        <v>17849.4637342208</v>
       </c>
       <c r="E3" t="n">
-        <v>162.865340744446</v>
+        <v>160.07463397273</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
